--- a/storage/app/pdfs/profiles_asia_download.xlsx
+++ b/storage/app/pdfs/profiles_asia_download.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Asia Africa/1. Informacion AsiaAfrica/1. Profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{B1BD5820-DD90-F543-A401-53E7C7F6D1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C807DBCB-981A-A247-9CAC-472ED1FB7214}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="8_{B1BD5820-DD90-F543-A401-53E7C7F6D1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{030E0BB4-D059-354D-ACF5-25D6A0DE732B}"/>
   <bookViews>
     <workbookView xWindow="4980" yWindow="5520" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="3" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="64">
   <si>
     <t>Content</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Malaysia</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
   </si>
   <si>
     <t>South Korea</t>
@@ -1051,7 +1048,7 @@
   <sheetPr>
     <tabColor rgb="FF002F60"/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="80.83203125" style="6" bestFit="1" customWidth="1"/>
@@ -1121,9 +1118,7 @@
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="A15" s="10"/>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
@@ -1184,9 +1179,6 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A36" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1195,11 +1187,10 @@
   <hyperlinks>
     <hyperlink ref="A9" location="Japan!A1" display="Japan" xr:uid="{52F41C02-FB17-40E8-9576-770EFBC6C47F}"/>
     <hyperlink ref="A10" location="Malaysia!A1" display="Malaysia" xr:uid="{6F0D300B-3674-44F3-860D-53DBFD4A4C07}"/>
-    <hyperlink ref="A11" location="Nigeria!A1" display="Nigeria" xr:uid="{84C30D8F-C4FA-4E9E-9E02-0CF531E6F6A7}"/>
-    <hyperlink ref="A12" location="'South Korea'!A1" display="South Korea" xr:uid="{652D061D-962D-4590-BBB9-43E1018ED83F}"/>
-    <hyperlink ref="A13" location="Taiwan!A1" display="Taiwan" xr:uid="{8CFC9BDF-65CB-434D-AF2C-C796AD422BEA}"/>
-    <hyperlink ref="A14" location="Thailand!A1" display="Thailand" xr:uid="{2F667091-2D0F-4D5F-8738-53AB376E7F72}"/>
-    <hyperlink ref="A15" location="Vietnam!A1" display="Vietnam" xr:uid="{4A147E18-6BA9-4E62-A7AB-14236C01CD13}"/>
+    <hyperlink ref="A11" location="'South Korea'!A1" display="South Korea" xr:uid="{652D061D-962D-4590-BBB9-43E1018ED83F}"/>
+    <hyperlink ref="A12" location="Taiwan!A1" display="Taiwan" xr:uid="{8CFC9BDF-65CB-434D-AF2C-C796AD422BEA}"/>
+    <hyperlink ref="A13" location="Thailand!A1" display="Thailand" xr:uid="{2F667091-2D0F-4D5F-8738-53AB376E7F72}"/>
+    <hyperlink ref="A14" location="Vietnam!A1" display="Vietnam" xr:uid="{4A147E18-6BA9-4E62-A7AB-14236C01CD13}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1257,10 +1248,10 @@
     </row>
     <row r="5" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="40"/>
       <c r="D5" s="40"/>
@@ -1277,7 +1268,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="39">
         <v>2023</v>
@@ -1297,7 +1288,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="41" t="s">
         <v>4</v>
@@ -1318,22 +1309,22 @@
     </row>
     <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>16</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="44"/>
       <c r="F8" s="43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="44"/>
       <c r="H8" s="43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="44"/>
       <c r="J8" s="17"/>
@@ -1352,28 +1343,28 @@
     <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>21</v>
-      </c>
       <c r="H9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>20</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>21</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -1390,7 +1381,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="20">
         <v>89</v>
@@ -1423,7 +1414,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="23"/>
@@ -1448,7 +1439,7 @@
     </row>
     <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -1473,7 +1464,7 @@
     </row>
     <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="26">
@@ -1506,23 +1497,23 @@
     </row>
     <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="27"/>
       <c r="C14" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="27"/>
       <c r="G14" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
@@ -1539,23 +1530,23 @@
     </row>
     <row r="15" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -1572,23 +1563,23 @@
     </row>
     <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="24"/>
       <c r="I16" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -1605,23 +1596,23 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="24"/>
       <c r="I17" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -1637,7 +1628,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24">
@@ -1669,7 +1660,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24">
@@ -1705,7 +1696,7 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="21">
@@ -1731,7 +1722,7 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="24"/>
       <c r="C21" s="21">
@@ -1753,7 +1744,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="23">
         <v>44</v>
@@ -1787,7 +1778,7 @@
     </row>
     <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="23">
         <v>0</v>
@@ -1796,7 +1787,7 @@
         <v>88.74</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="23">
         <v>88.74</v>
@@ -1808,7 +1799,7 @@
         <v>88.74</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I23" s="23">
         <v>88.74</v>
@@ -1821,10 +1812,10 @@
     </row>
     <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="36" t="s">
         <v>37</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>38</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="37"/>
@@ -1848,7 +1839,7 @@
     </row>
     <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -3068,10 +3059,10 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -3083,7 +3074,7 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="43">
         <v>2011</v>
@@ -3110,10 +3101,10 @@
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -3137,14 +3128,14 @@
     </row>
     <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="6"/>
@@ -3167,16 +3158,16 @@
     <row r="9" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>20</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>21</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -3197,7 +3188,7 @@
     </row>
     <row r="10" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="31">
         <v>95</v>
@@ -3226,7 +3217,7 @@
     </row>
     <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -3251,7 +3242,7 @@
     </row>
     <row r="12" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
@@ -3276,7 +3267,7 @@
     </row>
     <row r="13" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31">
@@ -3305,7 +3296,7 @@
     </row>
     <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31">
@@ -3334,7 +3325,7 @@
     </row>
     <row r="15" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31">
@@ -3363,7 +3354,7 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="33">
@@ -3387,7 +3378,7 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="33"/>
@@ -3407,7 +3398,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="34">
@@ -3431,7 +3422,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
@@ -3451,7 +3442,7 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -3471,7 +3462,7 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -3491,7 +3482,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="31">
         <v>60</v>
@@ -4809,7 +4800,7 @@
     </row>
     <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -4830,10 +4821,10 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -4850,7 +4841,7 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="43">
         <v>2009</v>
@@ -4877,10 +4868,10 @@
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -4904,14 +4895,14 @@
     </row>
     <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="17"/>
@@ -4934,16 +4925,16 @@
     <row r="9" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>20</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>21</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -4964,7 +4955,7 @@
     </row>
     <row r="10" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="31">
         <v>91</v>
@@ -4993,7 +4984,7 @@
     </row>
     <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -5018,7 +5009,7 @@
     </row>
     <row r="12" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
@@ -5043,7 +5034,7 @@
     </row>
     <row r="13" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31">
@@ -5072,7 +5063,7 @@
     </row>
     <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31">
@@ -5101,7 +5092,7 @@
     </row>
     <row r="15" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31">
@@ -5130,7 +5121,7 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="33">
@@ -5159,15 +5150,15 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -5188,7 +5179,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="34">
@@ -5217,7 +5208,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="31">
         <v>0.5</v>
@@ -5250,16 +5241,12 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="31"/>
-      <c r="C20" s="31" t="s">
-        <v>27</v>
-      </c>
+      <c r="C20" s="31"/>
       <c r="D20" s="31"/>
-      <c r="E20" s="31" t="s">
-        <v>27</v>
-      </c>
+      <c r="E20" s="31"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
@@ -5279,16 +5266,12 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="31"/>
-      <c r="C21" s="31" t="s">
-        <v>27</v>
-      </c>
+      <c r="C21" s="31"/>
       <c r="D21" s="31"/>
-      <c r="E21" s="31" t="s">
-        <v>27</v>
-      </c>
+      <c r="E21" s="31"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
@@ -5308,7 +5291,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31">
@@ -6671,7 +6654,7 @@
     </row>
     <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6692,10 +6675,10 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -6719,7 +6702,7 @@
     </row>
     <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="43">
         <v>2024</v>
@@ -6746,10 +6729,10 @@
     </row>
     <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -6766,18 +6749,18 @@
     </row>
     <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="44"/>
       <c r="F8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="45"/>
       <c r="H8" s="17"/>
@@ -6791,22 +6774,22 @@
     <row r="9" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="30" t="s">
         <v>20</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>21</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -6818,7 +6801,7 @@
     </row>
     <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="31">
         <v>92</v>
@@ -6842,7 +6825,7 @@
     </row>
     <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -6861,7 +6844,7 @@
     </row>
     <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
@@ -6886,7 +6869,7 @@
     </row>
     <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31">
@@ -6917,7 +6900,7 @@
     </row>
     <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31">
@@ -6948,7 +6931,7 @@
     </row>
     <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31">
@@ -6979,7 +6962,7 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="33"/>
@@ -7004,7 +6987,7 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
@@ -7029,7 +7012,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="34">
@@ -7060,7 +7043,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31">
@@ -7091,7 +7074,7 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31">
@@ -7122,7 +7105,7 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -7146,7 +7129,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="31">
         <v>45</v>
@@ -8116,7 +8099,7 @@
     </row>
     <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -8137,10 +8120,10 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="40"/>
       <c r="D5" s="40"/>
@@ -8157,7 +8140,7 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="39">
         <v>2014</v>
@@ -8184,10 +8167,10 @@
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -8211,18 +8194,18 @@
     </row>
     <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="44"/>
       <c r="F8" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="44"/>
       <c r="H8" s="17"/>
@@ -8243,22 +8226,22 @@
     <row r="9" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>20</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>21</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -8277,7 +8260,7 @@
     </row>
     <row r="10" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="20">
         <v>91</v>
@@ -8308,7 +8291,7 @@
     </row>
     <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="21">
         <v>80</v>
@@ -8339,7 +8322,7 @@
     </row>
     <row r="12" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -8364,7 +8347,7 @@
     </row>
     <row r="13" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="26">
@@ -8395,7 +8378,7 @@
     </row>
     <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="27"/>
       <c r="C14" s="21">
@@ -8426,7 +8409,7 @@
     </row>
     <row r="15" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="21">
@@ -8457,7 +8440,7 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24">
@@ -8488,7 +8471,7 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="24">
@@ -8519,7 +8502,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24">
@@ -8550,7 +8533,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -8575,7 +8558,7 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="21">
@@ -8606,10 +8589,10 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="46" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="46" t="s">
-        <v>47</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="46"/>
@@ -8633,7 +8616,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="24">
@@ -10000,7 +9983,7 @@
     </row>
     <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10021,10 +10004,10 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="47"/>
@@ -10041,7 +10024,7 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="47">
         <v>2023</v>
@@ -10068,10 +10051,10 @@
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="47"/>
@@ -10095,18 +10078,18 @@
     </row>
     <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="45"/>
       <c r="H8" s="17"/>
@@ -10127,22 +10110,22 @@
     <row r="9" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="30" t="s">
         <v>20</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>21</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -10161,7 +10144,7 @@
     </row>
     <row r="10" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="31">
         <v>92</v>
@@ -10192,18 +10175,18 @@
     </row>
     <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="17"/>
@@ -10223,18 +10206,18 @@
     </row>
     <row r="12" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="17"/>
@@ -10254,7 +10237,7 @@
     </row>
     <row r="13" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31">
@@ -10285,7 +10268,7 @@
     </row>
     <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31">
@@ -10316,7 +10299,7 @@
     </row>
     <row r="15" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31">
@@ -10347,7 +10330,7 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="33">
@@ -10378,7 +10361,7 @@
     </row>
     <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31">
@@ -10409,7 +10392,7 @@
     </row>
     <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="34">
@@ -10440,7 +10423,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31">
@@ -10471,19 +10454,19 @@
     </row>
     <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -10502,19 +10485,19 @@
     </row>
     <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -10533,7 +10516,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31">

--- a/storage/app/pdfs/profiles_asia_download.xlsx
+++ b/storage/app/pdfs/profiles_asia_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Asia Africa/1. Informacion AsiaAfrica/1. Profiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains Global Tool_016/Analisis/Asia/1. Informacion AsiaAfrica/1. Profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{B1BD5820-DD90-F543-A401-53E7C7F6D1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{030E0BB4-D059-354D-ACF5-25D6A0DE732B}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="8_{B1BD5820-DD90-F543-A401-53E7C7F6D1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29188E6E-7A7E-6A41-A30C-19CF18E1B530}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="5520" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="3" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="6260" yWindow="1700" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="67">
   <si>
     <t>Content</t>
   </si>
@@ -185,9 +185,6 @@
     <t>The approval of the Director General of the Department of Energy Business</t>
   </si>
   <si>
-    <t>Mobile Pollution Source Fuel Composition Control Standard Regulation</t>
-  </si>
-  <si>
     <t>Implementation Year</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>RON 94</t>
   </si>
   <si>
-    <t>MS 118-3:2011</t>
-  </si>
-  <si>
     <t>RON 95</t>
   </si>
   <si>
@@ -235,6 +229,21 @@
   <si>
     <t>RON 92</t>
   </si>
+  <si>
+    <t xml:space="preserve">Japan - JIS K 2202 </t>
+  </si>
+  <si>
+    <t>50 -&gt; 10</t>
+  </si>
+  <si>
+    <t>MS 118-3:2011 (Euro 4M → Euro 5M)</t>
+  </si>
+  <si>
+    <t>3.5 -&gt; 1</t>
+  </si>
+  <si>
+    <t>Mobile Pollution Source Fuel Composition Control Standard Regulation CNS 15037</t>
+  </si>
 </sst>
 </file>
 
@@ -245,7 +254,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,6 +353,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -516,7 +531,7 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -610,6 +625,15 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -634,20 +658,14 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1070,12 +1088,12 @@
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="38" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="35"/>
+      <c r="A6" s="38"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
@@ -1250,16 +1268,16 @@
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -1270,16 +1288,16 @@
       <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="42">
         <v>2023</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1290,16 +1308,16 @@
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
+      <c r="B7" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -1311,22 +1329,22 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="43" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="44"/>
-      <c r="H8" s="43" t="s">
+      <c r="G8" s="37"/>
+      <c r="H8" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="44"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
@@ -1814,16 +1832,16 @@
       <c r="A24" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="38"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
@@ -3061,12 +3079,12 @@
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
+      <c r="B5" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
@@ -3074,14 +3092,14 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="43">
+        <v>47</v>
+      </c>
+      <c r="B6" s="35">
         <v>2011</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -3103,12 +3121,12 @@
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -3130,14 +3148,14 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="45"/>
+      <c r="B8" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="36"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -3270,12 +3288,12 @@
         <v>24</v>
       </c>
       <c r="B13" s="31"/>
-      <c r="C13" s="31">
-        <v>1</v>
+      <c r="C13" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="D13" s="31"/>
-      <c r="E13" s="31">
-        <v>1</v>
+      <c r="E13" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -3396,17 +3414,17 @@
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="31"/>
-      <c r="C18" s="34">
-        <v>50</v>
+      <c r="C18" s="48" t="s">
+        <v>63</v>
       </c>
       <c r="D18" s="31"/>
-      <c r="E18" s="34">
-        <v>50</v>
+      <c r="E18" s="48" t="s">
+        <v>63</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
@@ -3422,7 +3440,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
@@ -3482,7 +3500,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="31">
         <v>60</v>
@@ -4823,12 +4841,12 @@
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
+      <c r="B5" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
@@ -4841,14 +4859,14 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="43">
+        <v>47</v>
+      </c>
+      <c r="B6" s="35">
         <v>2009</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
@@ -4870,12 +4888,12 @@
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
@@ -4897,14 +4915,14 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="45"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
@@ -5208,7 +5226,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="31">
         <v>0.5</v>
@@ -5291,7 +5309,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31">
@@ -6677,14 +6695,14 @@
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
+      <c r="B5" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -6702,16 +6720,16 @@
     </row>
     <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="43">
+        <v>47</v>
+      </c>
+      <c r="B6" s="35">
         <v>2024</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -6731,14 +6749,14 @@
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
@@ -6751,18 +6769,18 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="45"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -7043,7 +7061,7 @@
     </row>
     <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31">
@@ -7077,17 +7095,11 @@
         <v>32</v>
       </c>
       <c r="B20" s="31"/>
-      <c r="C20" s="31">
-        <v>10</v>
-      </c>
+      <c r="C20" s="31"/>
       <c r="D20" s="31"/>
-      <c r="E20" s="31">
-        <v>10</v>
-      </c>
+      <c r="E20" s="31"/>
       <c r="F20" s="31"/>
-      <c r="G20" s="31">
-        <v>10</v>
-      </c>
+      <c r="G20" s="31"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -7129,7 +7141,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="31">
         <v>45</v>
@@ -8122,14 +8134,14 @@
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -8142,14 +8154,14 @@
       <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="42">
         <v>2014</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -8169,14 +8181,14 @@
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
@@ -8196,18 +8208,18 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="43" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="44"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -10007,7 +10019,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="47"/>
@@ -10024,7 +10036,7 @@
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="47">
         <v>2023</v>
@@ -10054,7 +10066,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="47"/>
@@ -10080,18 +10092,18 @@
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="45"/>
+      <c r="B8" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="36"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -10456,18 +10468,18 @@
       <c r="A20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31" t="s">
-        <v>26</v>
-      </c>
+      <c r="B20" s="31">
+        <v>10</v>
+      </c>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31">
+        <v>10</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31">
+        <v>10</v>
+      </c>
+      <c r="G20" s="31"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -10516,7 +10528,7 @@
     </row>
     <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31">
